--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_AAC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_AAC.xlsx
@@ -663,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
         <v>12</v>
